--- a/Pipeline_Enterprise_PagBrasil_2026_v3.xlsx
+++ b/Pipeline_Enterprise_PagBrasil_2026_v3.xlsx
@@ -865,9 +865,9 @@
           <t>Cartão crédito/débito, Cartão Renner, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Click to Pay (confirmado); sem Apple Pay/Google Pay</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1025,9 +1025,9 @@
           <t>Cartão crédito/débito, Cartão C&amp;A, PIX, Boleto</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Google Pay (confirmado); PIX via Mercado Pago</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1345,9 +1345,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Não aceita (apenas crédito e PIX confirmados)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1505,9 +1505,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Não aceita (PIX e crédito apenas — sem Apple Pay/Google Pay)</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1585,9 +1585,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Natura Pay (conta digital própria para consultores); sem Apple Pay/Google Pay no site</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1665,9 +1665,9 @@
           <t>Cartão crédito/débito, PIX, Boleto</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>PayPal (confirmado); Mercado Pago (confirmado); sem Apple Pay/Google Pay no BR</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não confirmado (crédito e PIX apenas; PagStix loyalty program)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1905,9 +1905,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Não aceita (crédito Visa/Master/Amex/Elo/JCB, PIX e boleto apenas)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1985,9 +1985,9 @@
           <t>Cartão crédito/débito, PIX, Boleto</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Apple Pay; Samsung Pay (loja física confirmado — e-commerce a confirmar)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2225,9 +2225,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Leroy Merlin Pay (fintech própria com cartão Elo); sem Apple Pay/Google Pay</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2785,9 +2785,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Nupay (Nubank — confirmado); sem Apple Pay/Google Pay</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -3185,9 +3185,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Apple Pay; Google Pay (confirmado no site global — verificar .com.br)</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -3425,9 +3425,9 @@
           <t>Cartão crédito/débito, PIX, Boleto</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Apple Pay; Google Pay (site global levi.com confirma — verificar .com.br)</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -3585,9 +3585,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Não aceita (crédito, boleto e PIX apenas — sem carteiras digitais)</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -3665,9 +3665,9 @@
           <t>Cartão crédito/débito, PIX, Boleto, Parcelamento, Cartão Carrefour</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>A verificar</t>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Google Pay; Samsung Pay (via Cartão Carrefour Mastercard); Click to Pay</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>A verificar</t>
+          <t>Não confirmado (sem dados públicos de carteiras digitais)</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -4222,7 +4222,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Data de geração: 15/05/2026 20:11</t>
+          <t>Data de geração: 18/05/2026 18:28</t>
         </is>
       </c>
     </row>
